--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -334,43 +334,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -385,32 +348,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -418,21 +357,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -448,7 +372,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -463,7 +449,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -473,6 +459,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -487,7 +487,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,49 +553,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,25 +571,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,7 +595,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,73 +667,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,8 +684,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,6 +720,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -737,20 +757,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -769,15 +778,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,7 +786,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -795,7 +795,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -807,124 +807,124 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>19</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="R7">
         <v>50</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -320,67 +320,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -394,25 +342,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,9 +364,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -442,7 +411,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -453,6 +429,30 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -487,7 +487,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,73 +565,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,13 +583,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,73 +637,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -681,10 +681,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -705,37 +731,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -786,145 +786,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1641,7 +1641,7 @@
         <v>17</v>
       </c>
       <c r="M4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N4">
         <v>9</v>
@@ -1656,7 +1656,7 @@
         <v>25</v>
       </c>
       <c r="R4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="S4">
         <v>25</v>
@@ -2462,10 +2462,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N12">
         <v>18</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -321,14 +321,74 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -342,7 +402,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -358,28 +433,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,61 +441,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -458,7 +457,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -466,13 +473,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -487,7 +487,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,19 +571,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,151 +667,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,6 +678,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -699,18 +714,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -734,8 +738,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -757,27 +761,23 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,145 +786,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1553,7 +1553,7 @@
         <v>40</v>
       </c>
       <c r="R3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="S3">
         <v>70</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -320,10 +320,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -335,37 +335,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -378,25 +348,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -419,21 +386,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -447,9 +408,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -462,21 +477,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -484,6 +484,126 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -499,25 +619,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,121 +655,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,19 +667,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -681,17 +681,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -711,15 +705,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -731,15 +716,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -761,10 +737,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -778,6 +752,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,145 +786,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1471,13 +1471,13 @@
         <v>6</v>
       </c>
       <c r="Y2">
-        <v>-10</v>
+        <v>-88</v>
       </c>
       <c r="Z2">
-        <v>-54</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB2">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -320,9 +320,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -334,15 +334,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -355,23 +356,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,13 +388,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -417,14 +425,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -442,22 +442,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -477,6 +462,21 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -487,13 +487,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,43 +625,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,31 +637,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,85 +661,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,15 +678,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -701,6 +692,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,17 +735,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,9 +755,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -767,17 +778,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,145 +786,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="99">
   <si>
     <t>Id</t>
   </si>
@@ -115,6 +115,18 @@
     <t>Kind3</t>
   </si>
   <si>
+    <t>Y_Magic</t>
+  </si>
+  <si>
+    <t>X_Magic</t>
+  </si>
+  <si>
+    <t>L1_Magic</t>
+  </si>
+  <si>
+    <t>R1_Magic</t>
+  </si>
+  <si>
     <t>0001</t>
   </si>
   <si>
@@ -205,7 +217,7 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>ミカ</t>
+    <t>宝鐘マリン</t>
   </si>
   <si>
     <t>【煉獄棘姫】</t>
@@ -320,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -334,16 +346,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,24 +382,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -382,6 +393,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -401,13 +419,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -416,9 +427,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,14 +451,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -457,9 +460,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -471,8 +482,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -493,37 +505,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,25 +523,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,7 +553,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,25 +613,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,37 +655,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -661,13 +679,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -699,8 +711,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,30 +747,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -755,11 +758,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -778,6 +779,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,145 +798,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1286,15 +1298,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
+    <col min="6" max="6" width="9.09090909090909" customWidth="1"/>
     <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="6.18181818181818" customWidth="1"/>
+    <col min="9" max="9" width="6.81818181818182" customWidth="1"/>
+    <col min="10" max="10" width="6.45454545454545" customWidth="1"/>
+    <col min="11" max="11" width="6.63636363636364" customWidth="1"/>
+    <col min="12" max="13" width="7.09090909090909" customWidth="1"/>
+    <col min="14" max="14" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1394,8 +1414,20 @@
       <c r="AG1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1404,7 +1436,7 @@
       </c>
       <c r="C2" t="str">
         <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
-        <v>ミカ</v>
+        <v>宝鐘マリン</v>
       </c>
       <c r="D2" t="str">
         <f>INDEX(TextData!C:C,MATCH(B2,TextData!A:A))</f>
@@ -1417,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1497,8 +1529,20 @@
       <c r="AG2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="AH2">
+        <v>1010</v>
+      </c>
+      <c r="AI2">
+        <v>1060</v>
+      </c>
+      <c r="AJ2">
+        <v>100120</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1520,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1600,8 +1644,20 @@
       <c r="AG3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1623,7 +1679,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1703,8 +1759,20 @@
       <c r="AG4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1726,7 +1794,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1806,8 +1874,20 @@
       <c r="AG5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1829,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1909,8 +1989,20 @@
       <c r="AG6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1932,7 +2024,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2012,8 +2104,20 @@
       <c r="AG7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:33">
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2035,7 +2139,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2115,8 +2219,20 @@
       <c r="AG8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33">
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2138,7 +2254,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2218,8 +2334,20 @@
       <c r="AG9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33">
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2241,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2321,8 +2449,20 @@
       <c r="AG10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:33">
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2344,7 +2484,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2424,8 +2564,20 @@
       <c r="AG11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:33">
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2447,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2525,6 +2677,18 @@
         <v>0</v>
       </c>
       <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
         <v>0</v>
       </c>
     </row>
@@ -2546,13 +2710,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2560,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2604,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2645,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2686,7 +2850,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2727,7 +2891,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2768,7 +2932,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2809,7 +2973,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2850,7 +3014,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2891,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2932,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2973,7 +3137,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3026,16 +3190,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4613,13 +4777,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -4627,13 +4791,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -4641,13 +4805,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -4655,13 +4819,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -4669,13 +4833,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -4683,13 +4847,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -4697,13 +4861,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -4711,13 +4875,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -4725,13 +4889,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -4739,13 +4903,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -4753,13 +4917,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -4767,13 +4931,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -237,7 +237,7 @@
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
-    <t>アリエス</t>
+    <t>雪花ラミィ</t>
   </si>
   <si>
     <t>【怠惰な守護少女】</t>
@@ -247,7 +247,7 @@
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
-    <t>シイナ</t>
+    <t>博衣こより</t>
   </si>
   <si>
     <t>【イノセント・リメディ】</t>
@@ -332,9 +332,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -346,8 +346,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,22 +369,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -399,21 +407,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -427,9 +436,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -451,26 +460,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,9 +476,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,13 +499,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -517,25 +517,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,19 +559,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,13 +595,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -595,7 +631,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,79 +655,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,6 +690,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -708,11 +717,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -732,17 +747,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -752,15 +772,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -779,17 +790,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -798,145 +798,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C4" t="str">
         <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>アリエス</v>
+        <v>雪花ラミィ</v>
       </c>
       <c r="D4" t="str">
         <f>INDEX(TextData!C:C,MATCH(B4,TextData!A:A))</f>
@@ -1739,7 +1739,7 @@
         <v>-64</v>
       </c>
       <c r="AA4">
-        <v>0.82</v>
+        <v>2</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -1760,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>3020</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>100320</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C5" t="str">
         <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
-        <v>シイナ</v>
+        <v>博衣こより</v>
       </c>
       <c r="D5" t="str">
         <f>INDEX(TextData!C:C,MATCH(B5,TextData!A:A))</f>
@@ -1854,7 +1854,7 @@
         <v>-68</v>
       </c>
       <c r="AA5">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -1875,13 +1875,13 @@
         <v>0</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>4010</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>100420</v>
       </c>
       <c r="AK5">
         <v>0</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -332,10 +332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -346,16 +346,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,22 +383,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -398,31 +397,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -439,6 +415,14 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,7 +454,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,7 +499,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,37 +553,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,19 +571,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,24 +596,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,25 +625,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -661,25 +649,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -696,8 +696,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -718,6 +718,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -732,27 +747,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -761,17 +759,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -790,6 +779,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -798,145 +798,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1461,7 +1461,7 @@
         <v>39</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>30</v>
@@ -1576,7 +1576,7 @@
         <v>29</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>21</v>
@@ -1691,7 +1691,7 @@
         <v>35</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>17</v>
@@ -1806,7 +1806,7 @@
         <v>32</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -1921,7 +1921,7 @@
         <v>29</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -2036,7 +2036,7 @@
         <v>30</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>20</v>
@@ -2151,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>22</v>
@@ -2266,7 +2266,7 @@
         <v>37</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>15</v>
@@ -2381,7 +2381,7 @@
         <v>34</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>25</v>
@@ -2496,7 +2496,7 @@
         <v>30</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>17</v>
@@ -2611,7 +2611,7 @@
         <v>33</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>21</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="95">
   <si>
     <t>Id</t>
   </si>
@@ -113,18 +113,6 @@
   </si>
   <si>
     <t>Kind3</t>
-  </si>
-  <si>
-    <t>Y_Magic</t>
-  </si>
-  <si>
-    <t>X_Magic</t>
-  </si>
-  <si>
-    <t>L1_Magic</t>
-  </si>
-  <si>
-    <t>R1_Magic</t>
   </si>
   <si>
     <t>0001</t>
@@ -333,9 +321,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -343,14 +331,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +342,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -375,15 +385,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -397,15 +401,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -420,16 +432,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -446,31 +457,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,8 +470,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -499,31 +487,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,7 +517,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,7 +571,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,13 +601,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,79 +619,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,13 +637,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,30 +678,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -732,17 +696,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,11 +716,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -782,11 +748,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -798,16 +786,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -816,127 +804,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1298,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
@@ -1314,7 +1302,7 @@
     <col min="14" max="14" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1414,20 +1402,8 @@
       <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37">
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1449,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1529,20 +1505,8 @@
       <c r="AG2">
         <v>0</v>
       </c>
-      <c r="AH2">
-        <v>1010</v>
-      </c>
-      <c r="AI2">
-        <v>1060</v>
-      </c>
-      <c r="AJ2">
-        <v>100120</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1564,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1644,20 +1608,8 @@
       <c r="AG3">
         <v>0</v>
       </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1679,7 +1631,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1759,20 +1711,8 @@
       <c r="AG4">
         <v>0</v>
       </c>
-      <c r="AH4">
-        <v>3010</v>
-      </c>
-      <c r="AI4">
-        <v>3020</v>
-      </c>
-      <c r="AJ4">
-        <v>100320</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1794,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1874,20 +1814,8 @@
       <c r="AG5">
         <v>0</v>
       </c>
-      <c r="AH5">
-        <v>4010</v>
-      </c>
-      <c r="AI5">
-        <v>4030</v>
-      </c>
-      <c r="AJ5">
-        <v>100420</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1909,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1989,20 +1917,8 @@
       <c r="AG6">
         <v>0</v>
       </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2024,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2104,20 +2020,8 @@
       <c r="AG7">
         <v>0</v>
       </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2139,7 +2043,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2219,20 +2123,8 @@
       <c r="AG8">
         <v>0</v>
       </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2254,7 +2146,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2334,20 +2226,8 @@
       <c r="AG9">
         <v>0</v>
       </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2369,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2449,20 +2329,8 @@
       <c r="AG10">
         <v>0</v>
       </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2484,7 +2352,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2564,20 +2432,8 @@
       <c r="AG11">
         <v>0</v>
       </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2599,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2677,18 +2533,6 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
         <v>0</v>
       </c>
     </row>
@@ -2710,13 +2554,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2724,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2768,7 +2612,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2809,7 +2653,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2850,7 +2694,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2891,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2932,7 +2776,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2973,7 +2817,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -3014,7 +2858,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -3055,7 +2899,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3096,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3137,7 +2981,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3190,16 +3034,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4777,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -4791,13 +4635,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -4805,13 +4649,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -4819,13 +4663,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -4833,13 +4677,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -4847,13 +4691,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -4861,13 +4705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" ht="52" spans="1:4">
@@ -4875,13 +4719,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" ht="52" spans="1:4">
@@ -4889,13 +4733,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="39" spans="1:4">
@@ -4903,13 +4747,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" ht="39" spans="1:4">
@@ -4917,13 +4761,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="52" spans="1:4">
@@ -4931,13 +4775,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7070"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -88,6 +88,9 @@
     <t>Element5</t>
   </si>
   <si>
+    <t>Element6</t>
+  </si>
+  <si>
     <t>X</t>
   </si>
   <si>
@@ -133,21 +136,6 @@
     <t>0006</t>
   </si>
   <si>
-    <t>0007</t>
-  </si>
-  <si>
-    <t>0008</t>
-  </si>
-  <si>
-    <t>0009</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>0011</t>
-  </si>
-  <si>
     <t>ActorId</t>
   </si>
   <si>
@@ -175,21 +163,6 @@
     <t>11,21,31,1010,1030,100610,100620</t>
   </si>
   <si>
-    <t>11,21,31,2010,2040,100710,100720</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3070,100810,100820</t>
-  </si>
-  <si>
-    <t>11,21,31,1010,1050,100910,100920</t>
-  </si>
-  <si>
-    <t>11,21,31,2010,2030,101010,101020</t>
-  </si>
-  <si>
-    <t>11,21,31,3010,3050,101110,101120</t>
-  </si>
-  <si>
     <t>TriggerType1</t>
   </si>
   <si>
@@ -205,114 +178,64 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>宝鐘マリン</t>
-  </si>
-  <si>
-    <t>【煉獄棘姫】</t>
+    <t>エリシャ</t>
+  </si>
+  <si>
+    <t>Alisha</t>
   </si>
   <si>
     <t>高い攻撃性能を持つアタッカー。
 全体的にステータスが高く、赤属性魔法を習得することでさらに攻撃性能を伸ばすことができる。</t>
   </si>
   <si>
-    <t>エリザベート</t>
-  </si>
-  <si>
-    <t>【ChargeCommander】</t>
+    <t>ソラ</t>
+  </si>
+  <si>
+    <t>Sora</t>
   </si>
   <si>
     <t>回避率を上げて攻撃を避けるアタッカー。
 打たれ弱いがSPDが高く、回避率をアップする雷属性魔法を習得しやすい。</t>
   </si>
   <si>
-    <t>雪花ラミィ</t>
-  </si>
-  <si>
-    <t>【怠惰な守護少女】</t>
+    <t>リジェ</t>
+  </si>
+  <si>
+    <t>Ligier</t>
   </si>
   <si>
     <t>相手の攻撃を跳ね返すディフェンダー。
 受けた攻撃ダメージの一部を跳ね返す「カウンターオーラ」を使うことができる。</t>
   </si>
   <si>
-    <t>博衣こより</t>
-  </si>
-  <si>
-    <t>【イノセント・リメディ】</t>
+    <t>ミシェル</t>
+  </si>
+  <si>
+    <t>Michelle</t>
   </si>
   <si>
     <t>回復に特化したヒーラー。
 全体的にステータスが低いが、味方のHpを回復する「ヒーリング」を使うことができる。</t>
   </si>
   <si>
-    <t>レダ</t>
-  </si>
-  <si>
-    <t>【Self-sacrifice】</t>
+    <t>シイナ</t>
+  </si>
+  <si>
+    <t>Shiina</t>
   </si>
   <si>
     <t>相手の攻撃性能を下げるジャマー。
 「シェイディークラウド」で味方が受けるダメージを抑えたり、「毒」でスリップダメージを与える魔法を使うことができる。</t>
   </si>
   <si>
-    <t>リシェリ</t>
-  </si>
-  <si>
-    <t>【Faked-Magician】</t>
+    <t>ルネ</t>
+  </si>
+  <si>
+    <t>Renee</t>
   </si>
   <si>
     <t>味方のCTを短縮することができるサポーター。
 CT（魔法を再使用するまでのターン数）を短縮しパーティ全体の補助をすることができる。</t>
-  </si>
-  <si>
-    <t>ユニ</t>
-  </si>
-  <si>
-    <t>【奇跡の乙女】</t>
-  </si>
-  <si>
-    <t>味方の行動待機時間を短くするサポーター。
-「アウトオブオーダー」で両隣に配置した味方の行動待機時間を短縮したり、味方のATK・DEFをアップするバフ魔法を使うことができる。</t>
-  </si>
-  <si>
-    <t>マリーベル</t>
-  </si>
-  <si>
-    <t>【唯心の在処】</t>
-  </si>
-  <si>
-    <t>味方の攻撃を代わりに受け持つディフェンダー。
-「アクアミラージュ」で一定回数攻撃を無効にしたり、味方の攻撃を代わりに受けパーティの生存率を上げることができる。</t>
-  </si>
-  <si>
-    <t>ナツキ</t>
-  </si>
-  <si>
-    <t>【黄昏ニヒリスト】</t>
-  </si>
-  <si>
-    <t>攻撃回数の多い攻撃性能を持つアタッカー。
-Hpが低いがATKが高く、攻撃回数の多い「フレイムレイン」を使うことができる。</t>
-  </si>
-  <si>
-    <t>メリアドール</t>
-  </si>
-  <si>
-    <t>【怨嗟の鎖】</t>
-  </si>
-  <si>
-    <t>SPD性能に特化したジャマー。
-「ショックインパルス」で相手を行動不可にすることができる。</t>
-  </si>
-  <si>
-    <t>セリナ</t>
-  </si>
-  <si>
-    <t>【氷雪の勿忘草】</t>
-  </si>
-  <si>
-    <t>凍結攻撃を主体とするアタッカー。
-「ディープフリーズ」で攻撃時に一定量のダメージを受ける「凍結」状態にし、凍結効果をさらにアップすることで自滅に追い込むことができる。</t>
   </si>
 </sst>
 </file>
@@ -320,10 +243,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -335,7 +258,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,9 +309,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -365,37 +333,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -403,7 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -416,14 +354,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -432,15 +362,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -457,7 +388,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -465,14 +396,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -487,13 +410,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,6 +446,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -523,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,13 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,19 +542,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,73 +578,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,19 +590,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,6 +601,32 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -698,10 +647,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -710,23 +657,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -745,39 +701,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -786,145 +709,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1286,8 +1209,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="6"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
@@ -1302,7 +1225,7 @@
     <col min="14" max="14" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1402,8 +1325,11 @@
       <c r="AG1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1412,11 +1338,11 @@
       </c>
       <c r="C2" t="str">
         <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
-        <v>宝鐘マリン</v>
+        <v>エリシャ</v>
       </c>
       <c r="D2" t="str">
         <f>INDEX(TextData!C:C,MATCH(B2,TextData!A:A))</f>
-        <v>【煉獄棘姫】</v>
+        <v>Alisha</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1425,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1452,7 +1378,7 @@
         <v>55</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <v>60</v>
@@ -1467,37 +1393,37 @@
         <v>1</v>
       </c>
       <c r="U2">
+        <v>4</v>
+      </c>
+      <c r="V2">
+        <v>4</v>
+      </c>
+      <c r="W2">
+        <v>5</v>
+      </c>
+      <c r="X2">
+        <v>5</v>
+      </c>
+      <c r="Y2">
         <v>2</v>
       </c>
-      <c r="V2">
-        <v>6</v>
-      </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
-      <c r="X2">
-        <v>6</v>
-      </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>-88</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>24</v>
       </c>
-      <c r="AA2">
-        <v>1.25</v>
-      </c>
       <c r="AB2">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1505,8 +1431,11 @@
       <c r="AG2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:33">
+      <c r="AH2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1515,11 +1444,11 @@
       </c>
       <c r="C3" t="str">
         <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
-        <v>エリザベート</v>
+        <v>ソラ</v>
       </c>
       <c r="D3" t="str">
         <f>INDEX(TextData!C:C,MATCH(B3,TextData!A:A))</f>
-        <v>【ChargeCommander】</v>
+        <v>Sora</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1528,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1555,7 +1484,7 @@
         <v>60</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>40</v>
@@ -1567,40 +1496,40 @@
         <v>70</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W3">
         <v>7</v>
       </c>
       <c r="X3">
+        <v>2</v>
+      </c>
+      <c r="Y3">
         <v>3</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>-20</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>-52</v>
       </c>
-      <c r="AA3">
-        <v>0.71</v>
-      </c>
       <c r="AB3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1608,8 +1537,11 @@
       <c r="AG3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:33">
+      <c r="AH3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1618,11 +1550,11 @@
       </c>
       <c r="C4" t="str">
         <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>雪花ラミィ</v>
+        <v>リジェ</v>
       </c>
       <c r="D4" t="str">
         <f>INDEX(TextData!C:C,MATCH(B4,TextData!A:A))</f>
-        <v>【怠惰な守護少女】</v>
+        <v>Ligier</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1631,7 +1563,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1640,37 +1572,37 @@
         <v>99</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M4">
         <v>17</v>
       </c>
       <c r="N4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O4">
         <v>85</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R4">
         <v>50</v>
       </c>
       <c r="S4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4">
         <v>6</v>
@@ -1682,28 +1614,28 @@
         <v>2</v>
       </c>
       <c r="X4">
+        <v>3</v>
+      </c>
+      <c r="Y4">
         <v>6</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>-10</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>-64</v>
       </c>
-      <c r="AA4">
-        <v>2</v>
-      </c>
       <c r="AB4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1711,8 +1643,11 @@
       <c r="AG4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:33">
+      <c r="AH4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1721,11 +1656,11 @@
       </c>
       <c r="C5" t="str">
         <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
-        <v>博衣こより</v>
+        <v>ミシェル</v>
       </c>
       <c r="D5" t="str">
         <f>INDEX(TextData!C:C,MATCH(B5,TextData!A:A))</f>
-        <v>【イノセント・リメディ】</v>
+        <v>Michelle</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1734,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1761,7 +1696,7 @@
         <v>85</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>35</v>
@@ -1773,13 +1708,13 @@
         <v>30</v>
       </c>
       <c r="T5">
+        <v>7</v>
+      </c>
+      <c r="U5">
         <v>4</v>
       </c>
-      <c r="U5">
-        <v>3</v>
-      </c>
       <c r="V5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>1</v>
@@ -1788,25 +1723,25 @@
         <v>7</v>
       </c>
       <c r="Y5">
+        <v>7</v>
+      </c>
+      <c r="Z5">
         <v>-4</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>-68</v>
       </c>
-      <c r="AA5">
-        <v>2</v>
-      </c>
       <c r="AB5">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1814,8 +1749,11 @@
       <c r="AG5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:33">
+      <c r="AH5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1824,11 +1762,11 @@
       </c>
       <c r="C6" t="str">
         <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
-        <v>レダ</v>
+        <v>シイナ</v>
       </c>
       <c r="D6" t="str">
         <f>INDEX(TextData!C:C,MATCH(B6,TextData!A:A))</f>
-        <v>【Self-sacrifice】</v>
+        <v>Shiina</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1837,7 +1775,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1864,7 +1802,7 @@
         <v>70</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>30</v>
@@ -1876,40 +1814,40 @@
         <v>45</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>2</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
+        <v>3</v>
+      </c>
+      <c r="Z6">
         <v>-8</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>-44</v>
       </c>
-      <c r="AA6">
-        <v>0.82</v>
-      </c>
       <c r="AB6">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1917,8 +1855,11 @@
       <c r="AG6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:33">
+      <c r="AH6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1927,11 +1868,11 @@
       </c>
       <c r="C7" t="str">
         <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>リシェリ</v>
+        <v>ルネ</v>
       </c>
       <c r="D7" t="str">
         <f>INDEX(TextData!C:C,MATCH(B7,TextData!A:A))</f>
-        <v>【Faked-Magician】</v>
+        <v>Renee</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1940,7 +1881,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1967,7 +1908,7 @@
         <v>40</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>50</v>
@@ -1979,40 +1920,40 @@
         <v>50</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
         <v>48</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>-68</v>
       </c>
-      <c r="AA7">
-        <v>0.76</v>
-      </c>
       <c r="AB7">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -2020,519 +1961,7 @@
       <c r="AG7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:33">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>ユニ</v>
-      </c>
-      <c r="D8" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B8,TextData!A:A))</f>
-        <v>【奇跡の乙女】</v>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>99</v>
-      </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
-      </c>
-      <c r="M8">
-        <v>18</v>
-      </c>
-      <c r="N8">
-        <v>16</v>
-      </c>
-      <c r="O8">
-        <v>65</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>45</v>
-      </c>
-      <c r="R8">
-        <v>40</v>
-      </c>
-      <c r="S8">
-        <v>30</v>
-      </c>
-      <c r="T8">
-        <v>4</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>4</v>
-      </c>
-      <c r="W8">
-        <v>3</v>
-      </c>
-      <c r="X8">
-        <v>4</v>
-      </c>
-      <c r="Y8">
-        <v>-20</v>
-      </c>
-      <c r="Z8">
-        <v>-60</v>
-      </c>
-      <c r="AA8">
-        <v>0.79</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>マリーベル</v>
-      </c>
-      <c r="D9" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B9,TextData!A:A))</f>
-        <v>【唯心の在処】</v>
-      </c>
-      <c r="E9">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>99</v>
-      </c>
-      <c r="J9">
-        <v>37</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <v>15</v>
-      </c>
-      <c r="M9">
-        <v>21</v>
-      </c>
-      <c r="N9">
-        <v>16</v>
-      </c>
-      <c r="O9">
-        <v>80</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>40</v>
-      </c>
-      <c r="R9">
-        <v>60</v>
-      </c>
-      <c r="S9">
-        <v>35</v>
-      </c>
-      <c r="T9">
-        <v>6</v>
-      </c>
-      <c r="U9">
-        <v>2</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>5</v>
-      </c>
-      <c r="X9">
-        <v>4</v>
-      </c>
-      <c r="Y9">
-        <v>-52</v>
-      </c>
-      <c r="Z9">
-        <v>-52</v>
-      </c>
-      <c r="AA9">
-        <v>0.8</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>ナツキ</v>
-      </c>
-      <c r="D10" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B10,TextData!A:A))</f>
-        <v>【黄昏ニヒリスト】</v>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>99</v>
-      </c>
-      <c r="J10">
-        <v>34</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-      <c r="L10">
-        <v>25</v>
-      </c>
-      <c r="M10">
-        <v>12</v>
-      </c>
-      <c r="N10">
-        <v>24</v>
-      </c>
-      <c r="O10">
-        <v>25</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>65</v>
-      </c>
-      <c r="R10">
-        <v>30</v>
-      </c>
-      <c r="S10">
-        <v>50</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>4</v>
-      </c>
-      <c r="V10">
-        <v>4</v>
-      </c>
-      <c r="W10">
-        <v>7</v>
-      </c>
-      <c r="X10">
-        <v>2</v>
-      </c>
-      <c r="Y10">
-        <v>-16</v>
-      </c>
-      <c r="Z10">
-        <v>-52</v>
-      </c>
-      <c r="AA10">
-        <v>0.75</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>メリアドール</v>
-      </c>
-      <c r="D11" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B11,TextData!A:A))</f>
-        <v>【怨嗟の鎖】</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>99</v>
-      </c>
-      <c r="J11">
-        <v>30</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <v>17</v>
-      </c>
-      <c r="M11">
-        <v>7</v>
-      </c>
-      <c r="N11">
-        <v>31</v>
-      </c>
-      <c r="O11">
-        <v>45</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>30</v>
-      </c>
-      <c r="R11">
-        <v>20</v>
-      </c>
-      <c r="S11">
-        <v>75</v>
-      </c>
-      <c r="T11">
-        <v>4</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>6</v>
-      </c>
-      <c r="W11">
-        <v>5</v>
-      </c>
-      <c r="X11">
-        <v>2</v>
-      </c>
-      <c r="Y11">
-        <v>12</v>
-      </c>
-      <c r="Z11">
-        <v>-64</v>
-      </c>
-      <c r="AA11">
-        <v>0.77</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>セリナ</v>
-      </c>
-      <c r="D12" t="str">
-        <f>INDEX(TextData!C:C,MATCH(B12,TextData!A:A))</f>
-        <v>【氷雪の勿忘草】</v>
-      </c>
-      <c r="E12">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>99</v>
-      </c>
-      <c r="J12">
-        <v>33</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12">
-        <v>21</v>
-      </c>
-      <c r="M12">
-        <v>16</v>
-      </c>
-      <c r="N12">
-        <v>18</v>
-      </c>
-      <c r="O12">
-        <v>65</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>40</v>
-      </c>
-      <c r="R12">
-        <v>25</v>
-      </c>
-      <c r="S12">
-        <v>30</v>
-      </c>
-      <c r="T12">
-        <v>6</v>
-      </c>
-      <c r="U12">
-        <v>6</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>3</v>
-      </c>
-      <c r="X12">
-        <v>2</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>-54</v>
-      </c>
-      <c r="AA12">
-        <v>0.87</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
+      <c r="AH7">
         <v>0</v>
       </c>
     </row>
@@ -2546,7 +1975,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="44.2727272727273" customWidth="1"/>
@@ -2554,13 +1983,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2568,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2612,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2653,7 +2082,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2694,7 +2123,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2735,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2776,7 +2205,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2809,211 +2238,6 @@
         <v>1070</v>
       </c>
       <c r="C25">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>7</v>
-      </c>
-      <c r="B27">
-        <v>12090</v>
-      </c>
-      <c r="C27">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>7</v>
-      </c>
-      <c r="B28">
-        <v>412090</v>
-      </c>
-      <c r="C28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29">
-        <v>7</v>
-      </c>
-      <c r="B29">
-        <v>2050</v>
-      </c>
-      <c r="C29">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
-        <v>8</v>
-      </c>
-      <c r="B31">
-        <v>13060</v>
-      </c>
-      <c r="C31">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32">
-        <v>8</v>
-      </c>
-      <c r="B32">
-        <v>403070</v>
-      </c>
-      <c r="C32">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
-        <v>8</v>
-      </c>
-      <c r="B33">
-        <v>3060</v>
-      </c>
-      <c r="C33">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35">
-        <v>9</v>
-      </c>
-      <c r="B35">
-        <v>11070</v>
-      </c>
-      <c r="C35">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36">
-        <v>9</v>
-      </c>
-      <c r="B36">
-        <v>401050</v>
-      </c>
-      <c r="C36">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37">
-        <v>9</v>
-      </c>
-      <c r="B37">
-        <v>1080</v>
-      </c>
-      <c r="C37">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
-        <v>10</v>
-      </c>
-      <c r="B39">
-        <v>12010</v>
-      </c>
-      <c r="C39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>10</v>
-      </c>
-      <c r="B40">
-        <v>402030</v>
-      </c>
-      <c r="C40">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41">
-        <v>10</v>
-      </c>
-      <c r="B41">
-        <v>2080</v>
-      </c>
-      <c r="C41">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>11</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43">
-        <v>11</v>
-      </c>
-      <c r="B43">
-        <v>13090</v>
-      </c>
-      <c r="C43">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
-        <v>11</v>
-      </c>
-      <c r="B44">
-        <v>403050</v>
-      </c>
-      <c r="C44">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
-        <v>11</v>
-      </c>
-      <c r="B45">
-        <v>3080</v>
-      </c>
-      <c r="C45">
         <v>41</v>
       </c>
     </row>
@@ -3026,7 +2250,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="4" width="12.9090909090909" customWidth="1"/>
@@ -3034,16 +2258,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3883,720 +3107,6 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62">
-        <v>7</v>
-      </c>
-      <c r="B62">
-        <v>2040</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63">
-        <v>7</v>
-      </c>
-      <c r="B63">
-        <v>100720</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64">
-        <v>7</v>
-      </c>
-      <c r="B64">
-        <v>2010</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65">
-        <v>7</v>
-      </c>
-      <c r="B65">
-        <v>100710</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66">
-        <v>7</v>
-      </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67">
-        <v>7</v>
-      </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68">
-        <v>7</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69">
-        <v>7</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70">
-        <v>7</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71">
-        <v>7</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72">
-        <v>8</v>
-      </c>
-      <c r="B72">
-        <v>100820</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73">
-        <v>8</v>
-      </c>
-      <c r="B73">
-        <v>3070</v>
-      </c>
-      <c r="C73">
-        <v>14114</v>
-      </c>
-      <c r="D73">
-        <v>9120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74">
-        <v>8</v>
-      </c>
-      <c r="B74">
-        <v>3010</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75">
-        <v>8</v>
-      </c>
-      <c r="B75">
-        <v>100810</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76">
-        <v>8</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77">
-        <v>8</v>
-      </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-      <c r="C77">
-        <v>0</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78">
-        <v>8</v>
-      </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79">
-        <v>8</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80">
-        <v>8</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
-      </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81">
-        <v>8</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="C81">
-        <v>0</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82">
-        <v>9</v>
-      </c>
-      <c r="B82">
-        <v>100920</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83">
-        <v>9</v>
-      </c>
-      <c r="B83">
-        <v>1050</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84">
-        <v>9</v>
-      </c>
-      <c r="B84">
-        <v>1010</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85">
-        <v>9</v>
-      </c>
-      <c r="B85">
-        <v>100910</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86">
-        <v>9</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87">
-        <v>9</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88">
-        <v>9</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89">
-        <v>9</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90">
-        <v>9</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91">
-        <v>9</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92">
-        <v>10</v>
-      </c>
-      <c r="B92">
-        <v>2030</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93">
-        <v>10</v>
-      </c>
-      <c r="B93">
-        <v>101020</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94">
-        <v>10</v>
-      </c>
-      <c r="B94">
-        <v>2010</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95">
-        <v>10</v>
-      </c>
-      <c r="B95">
-        <v>101010</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96">
-        <v>10</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-      <c r="C96">
-        <v>0</v>
-      </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97">
-        <v>10</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
-      </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98">
-        <v>10</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="C98">
-        <v>0</v>
-      </c>
-      <c r="D98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99">
-        <v>10</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100">
-        <v>10</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101">
-        <v>10</v>
-      </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102">
-        <v>11</v>
-      </c>
-      <c r="B102">
-        <v>3050</v>
-      </c>
-      <c r="C102">
-        <v>6712</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103">
-        <v>11</v>
-      </c>
-      <c r="B103">
-        <v>101120</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-      <c r="D103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104">
-        <v>11</v>
-      </c>
-      <c r="B104">
-        <v>3010</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
-      </c>
-      <c r="D104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105">
-        <v>11</v>
-      </c>
-      <c r="B105">
-        <v>101110</v>
-      </c>
-      <c r="C105">
-        <v>0</v>
-      </c>
-      <c r="D105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106">
-        <v>11</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-      <c r="C106">
-        <v>0</v>
-      </c>
-      <c r="D106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107">
-        <v>11</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-      <c r="C107">
-        <v>0</v>
-      </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108">
-        <v>11</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="C108">
-        <v>0</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109">
-        <v>11</v>
-      </c>
-      <c r="B109">
-        <v>0</v>
-      </c>
-      <c r="C109">
-        <v>0</v>
-      </c>
-      <c r="D109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110">
-        <v>11</v>
-      </c>
-      <c r="B110">
-        <v>0</v>
-      </c>
-      <c r="C110">
-        <v>0</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111">
-        <v>11</v>
-      </c>
-      <c r="B111">
-        <v>0</v>
-      </c>
-      <c r="C111">
-        <v>0</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112">
-        <v>11</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
-      <c r="D112">
         <v>0</v>
       </c>
     </row>
@@ -4609,8 +3119,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
     <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
@@ -4621,13 +3131,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -4635,13 +3145,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -4649,13 +3159,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -4663,13 +3173,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -4677,13 +3187,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -4691,13 +3201,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -4705,83 +3215,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" ht="52" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" ht="52" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" ht="39" spans="1:4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" ht="39" spans="1:4">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" ht="52" spans="1:4">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -243,10 +243,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -257,85 +257,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -347,31 +273,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -386,6 +289,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -394,8 +312,90 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -410,7 +410,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +482,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +548,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,103 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,17 +604,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -626,6 +615,54 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,8 +684,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -662,45 +701,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,145 +709,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1572,34 +1572,34 @@
         <v>99</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="R4">
         <v>50</v>
       </c>
       <c r="S4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T4">
         <v>4</v>
@@ -1620,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>-10</v>
+        <v>-96</v>
       </c>
       <c r="AA4">
         <v>-64</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -151,7 +151,7 @@
     <t>11,21,31,2010,2070,100210,100220</t>
   </si>
   <si>
-    <t>11,21,31,3010,3020,100310,100320</t>
+    <t>11,21,31,3010,3110,100310,100320</t>
   </si>
   <si>
     <t>11,21,31,4010,4030,100410,100420</t>
@@ -243,10 +243,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -257,8 +257,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -273,19 +280,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -296,17 +294,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,7 +326,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,24 +379,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -373,31 +393,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -407,6 +407,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -422,13 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +452,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,37 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,73 +572,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,19 +584,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,8 +622,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,30 +638,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -684,6 +660,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -692,15 +701,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,145 +709,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1566,13 +1566,13 @@
         <v>35</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>99</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -1581,10 +1581,10 @@
         <v>18</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="O4">
         <v>55</v>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Actors" sheetId="1" r:id="rId1"/>
@@ -243,9 +243,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -258,7 +258,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,23 +295,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,22 +304,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +326,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +334,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -349,55 +387,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -410,7 +410,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +476,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,25 +554,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +578,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,91 +590,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,17 +604,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,23 +633,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,8 +657,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,32 +701,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,145 +709,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Actors.xlsx
+++ b/Assets/Data/Actors.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -31,9 +31,6 @@
     <t>ClassId</t>
   </si>
   <si>
-    <t>UnitType</t>
-  </si>
-  <si>
     <t>ImagePath</t>
   </si>
   <si>
@@ -157,7 +154,7 @@
     <t>11,21,31,4010,4030,100410,100420</t>
   </si>
   <si>
-    <t>11,21,31,5010,5070,100510,100520</t>
+    <t>11,21,31,5010,100510,100520</t>
   </si>
   <si>
     <t>11,21,31,1010,1030,100610,100620</t>
@@ -243,9 +240,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -271,17 +268,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,8 +298,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,22 +323,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,37 +354,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -379,23 +369,30 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -416,55 +413,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +455,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,31 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,19 +509,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,31 +563,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,37 +601,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,17 +640,46 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -692,15 +698,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,145 +706,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1209,23 +1206,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="6"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="7.54545454545455" customWidth="1"/>
-    <col min="6" max="6" width="9.09090909090909" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="6.18181818181818" customWidth="1"/>
-    <col min="9" max="9" width="6.81818181818182" customWidth="1"/>
-    <col min="10" max="10" width="6.45454545454545" customWidth="1"/>
-    <col min="11" max="11" width="6.63636363636364" customWidth="1"/>
-    <col min="12" max="13" width="7.09090909090909" customWidth="1"/>
-    <col min="14" max="14" width="7.36363636363636" customWidth="1"/>
+    <col min="6" max="6" width="9" style="2"/>
+    <col min="7" max="7" width="6.18181818181818" customWidth="1"/>
+    <col min="8" max="8" width="6.81818181818182" customWidth="1"/>
+    <col min="9" max="9" width="6.45454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6.63636363636364" customWidth="1"/>
+    <col min="11" max="12" width="7.09090909090909" customWidth="1"/>
+    <col min="13" max="13" width="7.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1241,10 +1237,10 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
@@ -1325,11 +1321,8 @@
       <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34">
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1347,83 +1340,83 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <v>99</v>
+      </c>
+      <c r="I2">
+        <v>39</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>12</v>
+      </c>
+      <c r="N2">
+        <v>60</v>
+      </c>
+      <c r="O2">
+        <v>100</v>
+      </c>
+      <c r="P2">
+        <v>60</v>
+      </c>
+      <c r="Q2">
+        <v>45</v>
+      </c>
+      <c r="R2">
+        <v>20</v>
+      </c>
+      <c r="S2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>99</v>
-      </c>
-      <c r="J2">
-        <v>39</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>30</v>
-      </c>
-      <c r="M2">
-        <v>15</v>
-      </c>
-      <c r="N2">
-        <v>15</v>
-      </c>
-      <c r="O2">
-        <v>55</v>
-      </c>
-      <c r="P2">
-        <v>100</v>
-      </c>
-      <c r="Q2">
-        <v>60</v>
-      </c>
-      <c r="R2">
-        <v>30</v>
-      </c>
-      <c r="S2">
-        <v>35</v>
-      </c>
       <c r="T2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U2">
         <v>4</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W2">
         <v>5</v>
       </c>
       <c r="X2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>2</v>
+        <v>-88</v>
       </c>
       <c r="Z2">
-        <v>-88</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>0.75</v>
       </c>
       <c r="AB2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1431,11 +1424,8 @@
       <c r="AG2">
         <v>0</v>
       </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34">
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1453,83 +1443,83 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>99</v>
+      </c>
+      <c r="I3">
+        <v>29</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>50</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>40</v>
+      </c>
+      <c r="Q3">
+        <v>20</v>
+      </c>
+      <c r="R3">
+        <v>40</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>99</v>
-      </c>
-      <c r="J3">
-        <v>29</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>21</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-      <c r="N3">
-        <v>28</v>
-      </c>
-      <c r="O3">
-        <v>60</v>
-      </c>
-      <c r="P3">
-        <v>100</v>
-      </c>
-      <c r="Q3">
-        <v>40</v>
-      </c>
-      <c r="R3">
-        <v>25</v>
-      </c>
-      <c r="S3">
-        <v>70</v>
-      </c>
-      <c r="T3">
-        <v>4</v>
-      </c>
       <c r="U3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V3">
         <v>7</v>
       </c>
       <c r="W3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>-20</v>
       </c>
       <c r="Z3">
-        <v>-20</v>
+        <v>-52</v>
       </c>
       <c r="AA3">
-        <v>-52</v>
+        <v>0.75</v>
       </c>
       <c r="AB3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1537,11 +1527,8 @@
       <c r="AG3">
         <v>0</v>
       </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34">
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1559,83 +1546,83 @@
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>99</v>
+      </c>
+      <c r="I4">
         <v>35</v>
       </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-      <c r="I4">
-        <v>99</v>
-      </c>
       <c r="J4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L4">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N4">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="O4">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="Q4">
         <v>40</v>
       </c>
       <c r="R4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S4">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
         <v>6</v>
       </c>
-      <c r="V4">
+      <c r="Y4">
+        <v>-96</v>
+      </c>
+      <c r="Z4">
+        <v>-64</v>
+      </c>
+      <c r="AA4">
+        <v>0.75</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>1</v>
       </c>
-      <c r="W4">
-        <v>2</v>
-      </c>
-      <c r="X4">
-        <v>3</v>
-      </c>
-      <c r="Y4">
-        <v>6</v>
-      </c>
-      <c r="Z4">
-        <v>-96</v>
-      </c>
-      <c r="AA4">
-        <v>-64</v>
-      </c>
-      <c r="AB4">
-        <v>0.75</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
       <c r="AE4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -1643,11 +1630,8 @@
       <c r="AG4">
         <v>0</v>
       </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1665,83 +1649,83 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="H5">
+        <v>99</v>
+      </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>18</v>
+      </c>
+      <c r="N5">
+        <v>85</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>35</v>
+      </c>
+      <c r="Q5">
+        <v>60</v>
+      </c>
+      <c r="R5">
+        <v>20</v>
+      </c>
+      <c r="S5">
+        <v>7</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>7</v>
+      </c>
+      <c r="V5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>99</v>
-      </c>
-      <c r="J5">
-        <v>32</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
-      <c r="M5">
+      <c r="W5">
         <v>7</v>
-      </c>
-      <c r="N5">
-        <v>21</v>
-      </c>
-      <c r="O5">
-        <v>85</v>
-      </c>
-      <c r="P5">
-        <v>100</v>
-      </c>
-      <c r="Q5">
-        <v>35</v>
-      </c>
-      <c r="R5">
-        <v>15</v>
-      </c>
-      <c r="S5">
-        <v>30</v>
-      </c>
-      <c r="T5">
-        <v>7</v>
-      </c>
-      <c r="U5">
-        <v>4</v>
-      </c>
-      <c r="V5">
-        <v>7</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="Z5">
-        <v>-4</v>
+        <v>-68</v>
       </c>
       <c r="AA5">
-        <v>-68</v>
+        <v>0.75</v>
       </c>
       <c r="AB5">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1749,11 +1733,8 @@
       <c r="AG5">
         <v>0</v>
       </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34">
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1771,83 +1752,83 @@
       <c r="E6">
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>99</v>
+      </c>
+      <c r="I6">
+        <v>29</v>
+      </c>
+      <c r="J6">
         <v>5</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>99</v>
-      </c>
-      <c r="J6">
-        <v>29</v>
-      </c>
       <c r="K6">
+        <v>16</v>
+      </c>
+      <c r="L6">
         <v>5</v>
       </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
       <c r="M6">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="N6">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>70</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
       <c r="Q6">
+        <v>45</v>
+      </c>
+      <c r="R6">
         <v>30</v>
       </c>
-      <c r="R6">
-        <v>40</v>
-      </c>
       <c r="S6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X6">
+        <v>3</v>
+      </c>
+      <c r="Y6">
+        <v>-8</v>
+      </c>
+      <c r="Z6">
+        <v>-44</v>
+      </c>
+      <c r="AA6">
+        <v>0.75</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
         <v>1</v>
       </c>
-      <c r="Y6">
-        <v>3</v>
-      </c>
-      <c r="Z6">
-        <v>-8</v>
-      </c>
-      <c r="AA6">
-        <v>-44</v>
-      </c>
-      <c r="AB6">
-        <v>0.75</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
       <c r="AE6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <v>0</v>
@@ -1855,11 +1836,8 @@
       <c r="AG6">
         <v>0</v>
       </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34">
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1877,47 +1855,47 @@
       <c r="E7">
         <v>6</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>99</v>
+      </c>
+      <c r="I7">
+        <v>30</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
+      </c>
+      <c r="N7">
+        <v>45</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>50</v>
+      </c>
+      <c r="Q7">
+        <v>30</v>
+      </c>
+      <c r="R7">
+        <v>30</v>
+      </c>
+      <c r="S7">
         <v>3</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>99</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
-      </c>
-      <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>19</v>
-      </c>
-      <c r="N7">
-        <v>20</v>
-      </c>
-      <c r="O7">
-        <v>40</v>
-      </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
-      <c r="Q7">
-        <v>50</v>
-      </c>
-      <c r="R7">
-        <v>50</v>
-      </c>
-      <c r="S7">
-        <v>50</v>
       </c>
       <c r="T7">
         <v>3</v>
@@ -1926,42 +1904,39 @@
         <v>3</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W7">
         <v>4</v>
       </c>
       <c r="X7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7">
+        <v>48</v>
+      </c>
+      <c r="Z7">
+        <v>-68</v>
+      </c>
+      <c r="AA7">
+        <v>0.75</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
         <v>1</v>
       </c>
-      <c r="Z7">
-        <v>48</v>
-      </c>
-      <c r="AA7">
-        <v>-68</v>
-      </c>
-      <c r="AB7">
-        <v>0.75</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
       <c r="AE7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
         <v>0</v>
       </c>
     </row>
@@ -1983,13 +1958,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>40</v>
-      </c>
-      <c r="C1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1997,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -2041,7 +2016,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2082,7 +2057,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2123,7 +2098,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2164,7 +2139,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2205,7 +2180,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2258,16 +2233,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" t="s">
-        <v>40</v>
-      </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
         <v>48</v>
-      </c>
-      <c r="D1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3131,13 +3106,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>51</v>
-      </c>
-      <c r="D1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" ht="39" spans="1:4">
@@ -3145,13 +3120,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:4">
@@ -3159,13 +3134,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" ht="39" spans="1:4">
@@ -3173,13 +3148,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:4">
@@ -3187,13 +3162,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" ht="52" spans="1:4">
@@ -3201,13 +3176,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" ht="39" spans="1:4">
@@ -3215,13 +3190,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
